--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3160"/>
+  <dimension ref="A1:F3161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63581,7 +63581,7 @@
         <v>98.34999999999999</v>
       </c>
       <c r="E3158" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F3158" t="n">
         <v>14489</v>
@@ -63618,13 +63618,33 @@
         <v>97.55</v>
       </c>
       <c r="D3160" t="n">
-        <v>97.15000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="E3160" t="n">
-        <v>97.25</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F3160" t="n">
-        <v>866</v>
+        <v>9495</v>
+      </c>
+    </row>
+    <row r="3161">
+      <c r="A3161" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B3161" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="C3161" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="D3161" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="E3161" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="F3161" t="n">
+        <v>1333</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3161"/>
+  <dimension ref="A1:F3162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63581,7 +63581,7 @@
         <v>98.34999999999999</v>
       </c>
       <c r="E3158" t="n">
-        <v>98.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="F3158" t="n">
         <v>14489</v>
@@ -63601,7 +63601,7 @@
         <v>97.2</v>
       </c>
       <c r="E3159" t="n">
-        <v>97.45</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="F3159" t="n">
         <v>18065</v>
@@ -63621,7 +63621,7 @@
         <v>96.7</v>
       </c>
       <c r="E3160" t="n">
-        <v>96.84999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="F3160" t="n">
         <v>9495</v>
@@ -63638,13 +63638,33 @@
         <v>96.90000000000001</v>
       </c>
       <c r="D3161" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E3161" t="n">
         <v>96.59999999999999</v>
       </c>
-      <c r="E3161" t="n">
-        <v>96.75</v>
-      </c>
       <c r="F3161" t="n">
-        <v>1333</v>
+        <v>9060</v>
+      </c>
+    </row>
+    <row r="3162">
+      <c r="A3162" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B3162" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="C3162" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3162" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="E3162" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="F3162" t="n">
+        <v>1019</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3162"/>
+  <dimension ref="A1:F3163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63658,13 +63658,33 @@
         <v>97</v>
       </c>
       <c r="D3162" t="n">
-        <v>96.5</v>
+        <v>96.3</v>
       </c>
       <c r="E3162" t="n">
-        <v>96.5</v>
+        <v>96.69</v>
       </c>
       <c r="F3162" t="n">
-        <v>1019</v>
+        <v>14104</v>
+      </c>
+    </row>
+    <row r="3163">
+      <c r="A3163" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B3163" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="C3163" t="n">
+        <v>97</v>
+      </c>
+      <c r="D3163" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E3163" t="n">
+        <v>97</v>
+      </c>
+      <c r="F3163" t="n">
+        <v>5036</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3163"/>
+  <dimension ref="A1:F3164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63661,7 +63661,7 @@
         <v>96.3</v>
       </c>
       <c r="E3162" t="n">
-        <v>96.69</v>
+        <v>96.95</v>
       </c>
       <c r="F3162" t="n">
         <v>14104</v>
@@ -63675,16 +63675,36 @@
         <v>96.90000000000001</v>
       </c>
       <c r="C3163" t="n">
-        <v>97</v>
+        <v>97.05</v>
       </c>
       <c r="D3163" t="n">
         <v>96.75</v>
       </c>
       <c r="E3163" t="n">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="F3163" t="n">
+        <v>13369</v>
+      </c>
+    </row>
+    <row r="3164">
+      <c r="A3164" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B3164" t="n">
         <v>97</v>
       </c>
-      <c r="F3163" t="n">
-        <v>5036</v>
+      <c r="C3164" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="D3164" t="n">
+        <v>97</v>
+      </c>
+      <c r="E3164" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="F3164" t="n">
+        <v>1401</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3164"/>
+  <dimension ref="A1:F3165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63661,7 +63661,7 @@
         <v>96.3</v>
       </c>
       <c r="E3162" t="n">
-        <v>96.95</v>
+        <v>96.69</v>
       </c>
       <c r="F3162" t="n">
         <v>14104</v>
@@ -63695,16 +63695,36 @@
         <v>97</v>
       </c>
       <c r="C3164" t="n">
-        <v>97.15000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D3164" t="n">
-        <v>97</v>
+        <v>96.95</v>
       </c>
       <c r="E3164" t="n">
-        <v>97.05</v>
+        <v>97.3</v>
       </c>
       <c r="F3164" t="n">
-        <v>1401</v>
+        <v>8443</v>
+      </c>
+    </row>
+    <row r="3165">
+      <c r="A3165" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3165" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="C3165" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="D3165" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="E3165" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="F3165" t="n">
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3165"/>
+  <dimension ref="A1:F3166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63718,13 +63718,33 @@
         <v>97.7</v>
       </c>
       <c r="D3165" t="n">
-        <v>97.3</v>
+        <v>97.2</v>
       </c>
       <c r="E3165" t="n">
-        <v>97.55</v>
+        <v>97.2</v>
       </c>
       <c r="F3165" t="n">
-        <v>130</v>
+        <v>7561</v>
+      </c>
+    </row>
+    <row r="3166">
+      <c r="A3166" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3166" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="C3166" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="D3166" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="E3166" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="F3166" t="n">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3166"/>
+  <dimension ref="A1:F3167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63681,7 +63681,7 @@
         <v>96.75</v>
       </c>
       <c r="E3163" t="n">
-        <v>96.90000000000001</v>
+        <v>96.95</v>
       </c>
       <c r="F3163" t="n">
         <v>13369</v>
@@ -63701,7 +63701,7 @@
         <v>96.95</v>
       </c>
       <c r="E3164" t="n">
-        <v>97.3</v>
+        <v>97.41</v>
       </c>
       <c r="F3164" t="n">
         <v>8443</v>
@@ -63738,13 +63738,33 @@
         <v>97.5</v>
       </c>
       <c r="D3166" t="n">
-        <v>97.2</v>
+        <v>96.8</v>
       </c>
       <c r="E3166" t="n">
-        <v>97.5</v>
+        <v>97.05</v>
       </c>
       <c r="F3166" t="n">
-        <v>36</v>
+        <v>9686</v>
+      </c>
+    </row>
+    <row r="3167">
+      <c r="A3167" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3167" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="C3167" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="D3167" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="E3167" t="n">
+        <v>97.05</v>
+      </c>
+      <c r="F3167" t="n">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3167"/>
+  <dimension ref="A1:F3168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63724,7 +63724,7 @@
         <v>97.2</v>
       </c>
       <c r="F3165" t="n">
-        <v>7561</v>
+        <v>6692</v>
       </c>
     </row>
     <row r="3166">
@@ -63744,7 +63744,7 @@
         <v>97.05</v>
       </c>
       <c r="F3166" t="n">
-        <v>9686</v>
+        <v>9676</v>
       </c>
     </row>
     <row r="3167">
@@ -63755,16 +63755,36 @@
         <v>97.05</v>
       </c>
       <c r="C3167" t="n">
-        <v>97.05</v>
+        <v>97.25</v>
       </c>
       <c r="D3167" t="n">
-        <v>97.05</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="E3167" t="n">
-        <v>97.05</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F3167" t="n">
-        <v>38</v>
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="3168">
+      <c r="A3168" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3168" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="C3168" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="D3168" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="E3168" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="F3168" t="n">
+        <v>221</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -63761,7 +63761,7 @@
         <v>96.84999999999999</v>
       </c>
       <c r="E3167" t="n">
-        <v>96.84999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="F3167" t="n">
         <v>1508</v>
@@ -63775,16 +63775,16 @@
         <v>96.84999999999999</v>
       </c>
       <c r="C3168" t="n">
-        <v>96.84999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="D3168" t="n">
-        <v>96.84999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="E3168" t="n">
-        <v>96.84999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="F3168" t="n">
-        <v>221</v>
+        <v>4467</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3168"/>
+  <dimension ref="A1:F3170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63724,7 +63724,7 @@
         <v>97.2</v>
       </c>
       <c r="F3165" t="n">
-        <v>6692</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="3166">
@@ -63785,6 +63785,46 @@
       </c>
       <c r="F3168" t="n">
         <v>4467</v>
+      </c>
+    </row>
+    <row r="3169">
+      <c r="A3169" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3169" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="C3169" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="D3169" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E3169" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="F3169" t="n">
+        <v>3334</v>
+      </c>
+    </row>
+    <row r="3170">
+      <c r="A3170" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3170" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="C3170" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="D3170" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="E3170" t="n">
+        <v>96.84999999999999</v>
+      </c>
+      <c r="F3170" t="n">
+        <v>790</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3170"/>
+  <dimension ref="A1:F3171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63724,7 +63724,7 @@
         <v>97.2</v>
       </c>
       <c r="F3165" t="n">
-        <v>7561</v>
+        <v>6692</v>
       </c>
     </row>
     <row r="3166">
@@ -63818,13 +63818,33 @@
         <v>96.84999999999999</v>
       </c>
       <c r="D3170" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="E3170" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F3170" t="n">
+        <v>3578</v>
+      </c>
+    </row>
+    <row r="3171">
+      <c r="A3171" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3171" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="C3171" t="n">
         <v>96.75</v>
       </c>
-      <c r="E3170" t="n">
-        <v>96.84999999999999</v>
-      </c>
-      <c r="F3170" t="n">
-        <v>790</v>
+      <c r="D3171" t="n">
+        <v>96.65000000000001</v>
+      </c>
+      <c r="E3171" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="F3171" t="n">
+        <v>1358</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3171"/>
+  <dimension ref="A1:F3172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63724,7 +63724,7 @@
         <v>97.2</v>
       </c>
       <c r="F3165" t="n">
-        <v>6692</v>
+        <v>7561</v>
       </c>
     </row>
     <row r="3166">
@@ -63744,7 +63744,7 @@
         <v>97.05</v>
       </c>
       <c r="F3166" t="n">
-        <v>9676</v>
+        <v>9686</v>
       </c>
     </row>
     <row r="3167">
@@ -63801,7 +63801,7 @@
         <v>96.75</v>
       </c>
       <c r="E3169" t="n">
-        <v>96.8</v>
+        <v>96.75</v>
       </c>
       <c r="F3169" t="n">
         <v>3334</v>
@@ -63821,7 +63821,7 @@
         <v>96.7</v>
       </c>
       <c r="E3170" t="n">
-        <v>96.7</v>
+        <v>96.8</v>
       </c>
       <c r="F3170" t="n">
         <v>3578</v>
@@ -63838,13 +63838,33 @@
         <v>96.75</v>
       </c>
       <c r="D3171" t="n">
-        <v>96.65000000000001</v>
+        <v>96.55</v>
       </c>
       <c r="E3171" t="n">
-        <v>96.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="F3171" t="n">
-        <v>1358</v>
+        <v>4401</v>
+      </c>
+    </row>
+    <row r="3172">
+      <c r="A3172" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B3172" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="C3172" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="D3172" t="n">
+        <v>94</v>
+      </c>
+      <c r="E3172" t="n">
+        <v>94.25</v>
+      </c>
+      <c r="F3172" t="n">
+        <v>23035</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3172"/>
+  <dimension ref="A1:F3173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63855,16 +63855,36 @@
         <v>94.25</v>
       </c>
       <c r="C3172" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="D3172" t="n">
-        <v>94</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="E3172" t="n">
-        <v>94.25</v>
+        <v>93.34999999999999</v>
       </c>
       <c r="F3172" t="n">
-        <v>23035</v>
+        <v>94805</v>
+      </c>
+    </row>
+    <row r="3173">
+      <c r="A3173" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3173" t="n">
+        <v>93.45</v>
+      </c>
+      <c r="C3173" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="D3173" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="E3173" t="n">
+        <v>93.2</v>
+      </c>
+      <c r="F3173" t="n">
+        <v>5001</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3173"/>
+  <dimension ref="A1:F3174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63878,13 +63878,33 @@
         <v>93.5</v>
       </c>
       <c r="D3173" t="n">
-        <v>93.2</v>
+        <v>91.95</v>
       </c>
       <c r="E3173" t="n">
-        <v>93.2</v>
+        <v>92</v>
       </c>
       <c r="F3173" t="n">
-        <v>5001</v>
+        <v>41557</v>
+      </c>
+    </row>
+    <row r="3174">
+      <c r="A3174" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3174" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="C3174" t="n">
+        <v>92.15000000000001</v>
+      </c>
+      <c r="D3174" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="E3174" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="F3174" t="n">
+        <v>11493</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3174"/>
+  <dimension ref="A1:F3175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63898,13 +63898,33 @@
         <v>92.15000000000001</v>
       </c>
       <c r="D3174" t="n">
-        <v>91.84999999999999</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="E3174" t="n">
-        <v>91.84999999999999</v>
+        <v>91</v>
       </c>
       <c r="F3174" t="n">
-        <v>11493</v>
+        <v>34588</v>
+      </c>
+    </row>
+    <row r="3175">
+      <c r="A3175" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B3175" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3175" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="D3175" t="n">
+        <v>91</v>
+      </c>
+      <c r="E3175" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="F3175" t="n">
+        <v>1340</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3175"/>
+  <dimension ref="A1:F3176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63915,16 +63915,36 @@
         <v>91</v>
       </c>
       <c r="C3175" t="n">
+        <v>91.59999999999999</v>
+      </c>
+      <c r="D3175" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E3175" t="n">
         <v>91.45</v>
       </c>
-      <c r="D3175" t="n">
-        <v>91</v>
-      </c>
-      <c r="E3175" t="n">
-        <v>91.40000000000001</v>
-      </c>
       <c r="F3175" t="n">
-        <v>1340</v>
+        <v>6638</v>
+      </c>
+    </row>
+    <row r="3176">
+      <c r="A3176" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B3176" t="n">
+        <v>91.7</v>
+      </c>
+      <c r="C3176" t="n">
+        <v>91.84999999999999</v>
+      </c>
+      <c r="D3176" t="n">
+        <v>91.45</v>
+      </c>
+      <c r="E3176" t="n">
+        <v>91.65000000000001</v>
+      </c>
+      <c r="F3176" t="n">
+        <v>644</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3176"/>
+  <dimension ref="A1:F3177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63938,13 +63938,33 @@
         <v>91.84999999999999</v>
       </c>
       <c r="D3176" t="n">
-        <v>91.45</v>
+        <v>90.95</v>
       </c>
       <c r="E3176" t="n">
-        <v>91.65000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="F3176" t="n">
-        <v>644</v>
+        <v>17208</v>
+      </c>
+    </row>
+    <row r="3177">
+      <c r="A3177" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3177" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="C3177" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="D3177" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="E3177" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="F3177" t="n">
+        <v>1820</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3177"/>
+  <dimension ref="A1:F3178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63958,13 +63958,33 @@
         <v>91.55</v>
       </c>
       <c r="D3177" t="n">
-        <v>91.05</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E3177" t="n">
-        <v>91.15000000000001</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="F3177" t="n">
-        <v>1820</v>
+        <v>3862</v>
+      </c>
+    </row>
+    <row r="3178">
+      <c r="A3178" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B3178" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="C3178" t="n">
+        <v>91.55</v>
+      </c>
+      <c r="D3178" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="E3178" t="n">
+        <v>91.5</v>
+      </c>
+      <c r="F3178" t="n">
+        <v>475</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3178"/>
+  <dimension ref="A1:F3179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63861,7 +63861,7 @@
         <v>93.15000000000001</v>
       </c>
       <c r="E3172" t="n">
-        <v>93.34999999999999</v>
+        <v>93.23999999999999</v>
       </c>
       <c r="F3172" t="n">
         <v>94805</v>
@@ -63881,7 +63881,7 @@
         <v>91.95</v>
       </c>
       <c r="E3173" t="n">
-        <v>92</v>
+        <v>92.34</v>
       </c>
       <c r="F3173" t="n">
         <v>41557</v>
@@ -63901,7 +63901,7 @@
         <v>90.84999999999999</v>
       </c>
       <c r="E3174" t="n">
-        <v>91</v>
+        <v>91.16</v>
       </c>
       <c r="F3174" t="n">
         <v>34588</v>
@@ -63921,7 +63921,7 @@
         <v>90.75</v>
       </c>
       <c r="E3175" t="n">
-        <v>91.45</v>
+        <v>91.5</v>
       </c>
       <c r="F3175" t="n">
         <v>6638</v>
@@ -63941,7 +63941,7 @@
         <v>90.95</v>
       </c>
       <c r="E3176" t="n">
-        <v>91.34999999999999</v>
+        <v>91.28</v>
       </c>
       <c r="F3176" t="n">
         <v>17208</v>
@@ -63961,7 +63961,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="E3177" t="n">
-        <v>91.34999999999999</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="F3177" t="n">
         <v>3862</v>
@@ -63975,16 +63975,36 @@
         <v>91.3</v>
       </c>
       <c r="C3178" t="n">
-        <v>91.55</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="D3178" t="n">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E3178" t="n">
-        <v>91.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="F3178" t="n">
-        <v>475</v>
+        <v>25392</v>
+      </c>
+    </row>
+    <row r="3179">
+      <c r="A3179" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B3179" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C3179" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="D3179" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E3179" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="F3179" t="n">
+        <v>7942</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3179"/>
+  <dimension ref="A1:F3180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63998,13 +63998,33 @@
         <v>91.2</v>
       </c>
       <c r="D3179" t="n">
-        <v>90.75</v>
+        <v>90.3</v>
       </c>
       <c r="E3179" t="n">
-        <v>90.75</v>
+        <v>90.5</v>
       </c>
       <c r="F3179" t="n">
-        <v>7942</v>
+        <v>22769</v>
+      </c>
+    </row>
+    <row r="3180">
+      <c r="A3180" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B3180" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="C3180" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3180" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="E3180" t="n">
+        <v>91</v>
+      </c>
+      <c r="F3180" t="n">
+        <v>3648</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3180"/>
+  <dimension ref="A1:F3181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63981,7 +63981,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="E3178" t="n">
-        <v>91.09999999999999</v>
+        <v>91.02</v>
       </c>
       <c r="F3178" t="n">
         <v>25392</v>
@@ -64001,7 +64001,7 @@
         <v>90.3</v>
       </c>
       <c r="E3179" t="n">
-        <v>90.5</v>
+        <v>90.45999999999999</v>
       </c>
       <c r="F3179" t="n">
         <v>22769</v>
@@ -64015,16 +64015,36 @@
         <v>90.8</v>
       </c>
       <c r="C3180" t="n">
-        <v>91</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="D3180" t="n">
         <v>90.65000000000001</v>
       </c>
       <c r="E3180" t="n">
-        <v>91</v>
+        <v>91.05</v>
       </c>
       <c r="F3180" t="n">
-        <v>3648</v>
+        <v>12059</v>
+      </c>
+    </row>
+    <row r="3181">
+      <c r="A3181" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B3181" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C3181" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D3181" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="E3181" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="F3181" t="n">
+        <v>1012</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3181"/>
+  <dimension ref="A1:F3182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64038,13 +64038,33 @@
         <v>91.09999999999999</v>
       </c>
       <c r="D3181" t="n">
-        <v>90.8</v>
+        <v>90.2</v>
       </c>
       <c r="E3181" t="n">
-        <v>90.8</v>
+        <v>90.95</v>
       </c>
       <c r="F3181" t="n">
-        <v>1012</v>
+        <v>10858</v>
+      </c>
+    </row>
+    <row r="3182">
+      <c r="A3182" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B3182" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="C3182" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="D3182" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="E3182" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="F3182" t="n">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3182"/>
+  <dimension ref="A1:F3183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64055,7 +64055,7 @@
         <v>90.95</v>
       </c>
       <c r="C3182" t="n">
-        <v>90.95</v>
+        <v>91.2</v>
       </c>
       <c r="D3182" t="n">
         <v>90.40000000000001</v>
@@ -64064,7 +64064,27 @@
         <v>90.7</v>
       </c>
       <c r="F3182" t="n">
-        <v>2025</v>
+        <v>11422</v>
+      </c>
+    </row>
+    <row r="3183">
+      <c r="A3183" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B3183" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="C3183" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="D3183" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="E3183" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="F3183" t="n">
+        <v>615</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3183"/>
+  <dimension ref="A1:F3184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64021,7 +64021,7 @@
         <v>90.65000000000001</v>
       </c>
       <c r="E3180" t="n">
-        <v>91.05</v>
+        <v>90.75</v>
       </c>
       <c r="F3180" t="n">
         <v>12059</v>
@@ -64041,7 +64041,7 @@
         <v>90.2</v>
       </c>
       <c r="E3181" t="n">
-        <v>90.95</v>
+        <v>90.61</v>
       </c>
       <c r="F3181" t="n">
         <v>10858</v>
@@ -64061,7 +64061,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="E3182" t="n">
-        <v>90.7</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="F3182" t="n">
         <v>11422</v>
@@ -64078,13 +64078,33 @@
         <v>90.8</v>
       </c>
       <c r="D3183" t="n">
-        <v>90.34999999999999</v>
+        <v>90.25</v>
       </c>
       <c r="E3183" t="n">
         <v>90.34999999999999</v>
       </c>
       <c r="F3183" t="n">
-        <v>615</v>
+        <v>6469</v>
+      </c>
+    </row>
+    <row r="3184">
+      <c r="A3184" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B3184" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="C3184" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="D3184" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="E3184" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="F3184" t="n">
+        <v>949</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3184"/>
+  <dimension ref="A1:F3185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64041,7 +64041,7 @@
         <v>90.2</v>
       </c>
       <c r="E3181" t="n">
-        <v>90.61</v>
+        <v>90.95</v>
       </c>
       <c r="F3181" t="n">
         <v>10858</v>
@@ -64061,7 +64061,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="E3182" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="F3182" t="n">
         <v>11422</v>
@@ -64095,16 +64095,36 @@
         <v>90.25</v>
       </c>
       <c r="C3184" t="n">
-        <v>90.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D3184" t="n">
         <v>90.2</v>
       </c>
       <c r="E3184" t="n">
-        <v>90.5</v>
+        <v>90.8</v>
       </c>
       <c r="F3184" t="n">
-        <v>949</v>
+        <v>20136</v>
+      </c>
+    </row>
+    <row r="3185">
+      <c r="A3185" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B3185" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="C3185" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D3185" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E3185" t="n">
+        <v>91.34999999999999</v>
+      </c>
+      <c r="F3185" t="n">
+        <v>2144</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3185"/>
+  <dimension ref="A1:F3186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64041,7 +64041,7 @@
         <v>90.2</v>
       </c>
       <c r="E3181" t="n">
-        <v>90.95</v>
+        <v>90.61</v>
       </c>
       <c r="F3181" t="n">
         <v>10858</v>
@@ -64061,7 +64061,7 @@
         <v>90.40000000000001</v>
       </c>
       <c r="E3182" t="n">
-        <v>90.7</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="F3182" t="n">
         <v>11422</v>
@@ -64115,16 +64115,36 @@
         <v>90.8</v>
       </c>
       <c r="C3185" t="n">
-        <v>91.40000000000001</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="D3185" t="n">
         <v>90.7</v>
       </c>
       <c r="E3185" t="n">
-        <v>91.34999999999999</v>
+        <v>91.05</v>
       </c>
       <c r="F3185" t="n">
-        <v>2144</v>
+        <v>8315</v>
+      </c>
+    </row>
+    <row r="3186">
+      <c r="A3186" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B3186" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="C3186" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="D3186" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="E3186" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="F3186" t="n">
+        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3186"/>
+  <dimension ref="A1:F3187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64081,7 +64081,7 @@
         <v>90.25</v>
       </c>
       <c r="E3183" t="n">
-        <v>90.34999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F3183" t="n">
         <v>6469</v>
@@ -64138,13 +64138,33 @@
         <v>91.25</v>
       </c>
       <c r="D3186" t="n">
-        <v>91.09999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="E3186" t="n">
-        <v>91.25</v>
+        <v>90.95</v>
       </c>
       <c r="F3186" t="n">
-        <v>307</v>
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="3187">
+      <c r="A3187" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B3187" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="C3187" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="D3187" t="n">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="E3187" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="F3187" t="n">
+        <v>109</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3187"/>
+  <dimension ref="A1:F3188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64081,7 +64081,7 @@
         <v>90.25</v>
       </c>
       <c r="E3183" t="n">
-        <v>90.3</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="F3183" t="n">
         <v>6469</v>
@@ -64161,10 +64161,30 @@
         <v>90.90000000000001</v>
       </c>
       <c r="E3187" t="n">
-        <v>91.15000000000001</v>
+        <v>90.95</v>
       </c>
       <c r="F3187" t="n">
-        <v>109</v>
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="3188">
+      <c r="A3188" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B3188" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="C3188" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="D3188" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="E3188" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="F3188" t="n">
+        <v>2457</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3188"/>
+  <dimension ref="A1:F3189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64081,7 +64081,7 @@
         <v>90.25</v>
       </c>
       <c r="E3183" t="n">
-        <v>90.34999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="F3183" t="n">
         <v>6469</v>
@@ -64101,7 +64101,7 @@
         <v>90.2</v>
       </c>
       <c r="E3184" t="n">
-        <v>90.8</v>
+        <v>90.97</v>
       </c>
       <c r="F3184" t="n">
         <v>20136</v>
@@ -64121,7 +64121,7 @@
         <v>90.7</v>
       </c>
       <c r="E3185" t="n">
-        <v>91.05</v>
+        <v>91.11</v>
       </c>
       <c r="F3185" t="n">
         <v>8315</v>
@@ -64175,16 +64175,36 @@
         <v>90.95</v>
       </c>
       <c r="C3188" t="n">
-        <v>90.95</v>
+        <v>91.05</v>
       </c>
       <c r="D3188" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="E3188" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F3188" t="n">
+        <v>6482</v>
+      </c>
+    </row>
+    <row r="3189">
+      <c r="A3189" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B3189" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="C3189" t="n">
         <v>90.7</v>
       </c>
-      <c r="E3188" t="n">
-        <v>90.7</v>
-      </c>
-      <c r="F3188" t="n">
-        <v>2457</v>
+      <c r="D3189" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="E3189" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="F3189" t="n">
+        <v>207</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3189"/>
+  <dimension ref="A1:F3190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64141,7 +64141,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="E3186" t="n">
-        <v>90.95</v>
+        <v>91.05</v>
       </c>
       <c r="F3186" t="n">
         <v>4251</v>
@@ -64195,16 +64195,36 @@
         <v>90.59999999999999</v>
       </c>
       <c r="C3189" t="n">
-        <v>90.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D3189" t="n">
         <v>90.45</v>
       </c>
       <c r="E3189" t="n">
-        <v>90.45</v>
+        <v>90.8</v>
       </c>
       <c r="F3189" t="n">
-        <v>207</v>
+        <v>3605</v>
+      </c>
+    </row>
+    <row r="3190">
+      <c r="A3190" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B3190" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="C3190" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="D3190" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="E3190" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F3190" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3190"/>
+  <dimension ref="A1:F3191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64161,7 +64161,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="E3187" t="n">
-        <v>90.95</v>
+        <v>90.92</v>
       </c>
       <c r="F3187" t="n">
         <v>2105</v>
@@ -64181,7 +64181,7 @@
         <v>90.34999999999999</v>
       </c>
       <c r="E3188" t="n">
-        <v>90.59999999999999</v>
+        <v>90.54000000000001</v>
       </c>
       <c r="F3188" t="n">
         <v>6482</v>
@@ -64215,16 +64215,36 @@
         <v>90.8</v>
       </c>
       <c r="C3190" t="n">
-        <v>90.8</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="D3190" t="n">
         <v>90.59999999999999</v>
       </c>
       <c r="E3190" t="n">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="F3190" t="n">
-        <v>55</v>
+        <v>5185</v>
+      </c>
+    </row>
+    <row r="3191">
+      <c r="A3191" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B3191" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="C3191" t="n">
+        <v>90.7</v>
+      </c>
+      <c r="D3191" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="E3191" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="F3191" t="n">
+        <v>739</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3191"/>
+  <dimension ref="A1:F3192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64238,13 +64238,33 @@
         <v>90.7</v>
       </c>
       <c r="D3191" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E3191" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="F3191" t="n">
+        <v>3158</v>
+      </c>
+    </row>
+    <row r="3192">
+      <c r="A3192" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B3192" t="n">
         <v>90.55</v>
       </c>
-      <c r="E3191" t="n">
+      <c r="C3192" t="n">
         <v>90.55</v>
       </c>
-      <c r="F3191" t="n">
-        <v>739</v>
+      <c r="D3192" t="n">
+        <v>90.45</v>
+      </c>
+      <c r="E3192" t="n">
+        <v>90.55</v>
+      </c>
+      <c r="F3192" t="n">
+        <v>361</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3192"/>
+  <dimension ref="A1:F3193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64255,16 +64255,36 @@
         <v>90.55</v>
       </c>
       <c r="C3192" t="n">
-        <v>90.55</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="D3192" t="n">
         <v>90.45</v>
       </c>
       <c r="E3192" t="n">
-        <v>90.55</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="F3192" t="n">
-        <v>361</v>
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="3193">
+      <c r="A3193" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B3193" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="C3193" t="n">
+        <v>90.8</v>
+      </c>
+      <c r="D3193" t="n">
+        <v>90.65000000000001</v>
+      </c>
+      <c r="E3193" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="F3193" t="n">
+        <v>3394</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3193"/>
+  <dimension ref="A1:F3194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64284,7 +64284,27 @@
         <v>90.75</v>
       </c>
       <c r="F3193" t="n">
-        <v>3394</v>
+        <v>6473</v>
+      </c>
+    </row>
+    <row r="3194">
+      <c r="A3194" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B3194" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="C3194" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D3194" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="E3194" t="n">
+        <v>91.05</v>
+      </c>
+      <c r="F3194" t="n">
+        <v>12836</v>
       </c>
     </row>
   </sheetData>

--- a/database/FEF1!.xlsx
+++ b/database/FEF1!.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3194"/>
+  <dimension ref="A1:F3195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64261,7 +64261,7 @@
         <v>90.45</v>
       </c>
       <c r="E3192" t="n">
-        <v>90.59999999999999</v>
+        <v>90.62</v>
       </c>
       <c r="F3192" t="n">
         <v>1049</v>
@@ -64298,13 +64298,33 @@
         <v>91.40000000000001</v>
       </c>
       <c r="D3194" t="n">
-        <v>90.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E3194" t="n">
-        <v>91.05</v>
+        <v>90.8</v>
       </c>
       <c r="F3194" t="n">
-        <v>12836</v>
+        <v>52729</v>
+      </c>
+    </row>
+    <row r="3195">
+      <c r="A3195" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B3195" t="n">
+        <v>91</v>
+      </c>
+      <c r="C3195" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="D3195" t="n">
+        <v>90.75</v>
+      </c>
+      <c r="E3195" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="F3195" t="n">
+        <v>17361</v>
       </c>
     </row>
   </sheetData>
